--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_42.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_42.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ExamPass?</t>
+          <t>DV</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Perfectionism</t>
+          <t>Sessions</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-1.004854045576298</v>
+        <v>1.242023260689646</v>
       </c>
       <c r="C2">
-        <v>0.04009765549851263</v>
+        <v>-0.1750743568826281</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.4480693434426529</v>
+        <v>0.9937187880650783</v>
       </c>
       <c r="C3">
-        <v>-0.8083585879831593</v>
+        <v>0.176399866524376</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.386639631313266</v>
+        <v>1.320099828022721</v>
       </c>
       <c r="C4">
-        <v>-0.6797975838429526</v>
+        <v>-0.466219061417568</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.4474067313594184</v>
+        <v>-0.7091344539087485</v>
       </c>
       <c r="C5">
-        <v>1.43812830329877</v>
+        <v>-0.00295730007439271</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.5158896950161364</v>
+        <v>-1.651268275751293</v>
       </c>
       <c r="C6">
-        <v>0.0491673862826536</v>
+        <v>0.2951559881004364</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>2.087718865941167</v>
+        <v>-0.9103261723084938</v>
       </c>
       <c r="C7">
-        <v>-0.4367302009257835</v>
+        <v>0.2701729517775263</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-1.472410739653517</v>
+        <v>-1.747774442255667</v>
       </c>
       <c r="C8">
-        <v>1.823016018728993</v>
+        <v>1.687965620474669</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.2702275914569685</v>
+        <v>-1.413058671764053</v>
       </c>
       <c r="C9">
-        <v>1.123834356945619</v>
+        <v>-0.1296389083416549</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-1.317706295494954</v>
+        <v>1.668075617425473</v>
       </c>
       <c r="C10">
-        <v>0.8924291314649404</v>
+        <v>-0.8764240611379041</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.7926322394147186</v>
+        <v>0.591439320921688</v>
       </c>
       <c r="C11">
-        <v>-1.188821626925995</v>
+        <v>-0.03724788197622717</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-2.036740757665517</v>
+        <v>0.986301432203359</v>
       </c>
       <c r="C12">
-        <v>0.5831756671960704</v>
+        <v>0.5349813187290486</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.5276411978051041</v>
+        <v>-0.1888924781981894</v>
       </c>
       <c r="C13">
-        <v>2.622498825573509</v>
+        <v>-1.682056529858602</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.3218314961815918</v>
+        <v>-0.3166584937970531</v>
       </c>
       <c r="C14">
-        <v>1.634045407606949</v>
+        <v>1.341127896885129</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.921233413297525</v>
+        <v>1.003794223374987</v>
       </c>
       <c r="C15">
-        <v>-0.7976562774991798</v>
+        <v>-1.096652576580094</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.4730070989531203</v>
+        <v>-0.3776943973739328</v>
       </c>
       <c r="C16">
-        <v>0.6602644583467012</v>
+        <v>1.575145934562615</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>2.12517766471094</v>
+        <v>-0.5213006308282583</v>
       </c>
       <c r="C17">
-        <v>-1.925857777330204</v>
+        <v>0.9563931479634283</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-2.025712991749244</v>
+        <v>0.1089623902126615</v>
       </c>
       <c r="C18">
-        <v>2.536700696845883</v>
+        <v>-0.9686690596357405</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-1.354663082038466</v>
+        <v>-0.7988861392059822</v>
       </c>
       <c r="C19">
-        <v>0.2584139445721111</v>
+        <v>-0.5815925879612429</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.8343787668734721</v>
+        <v>0.3787997594753208</v>
       </c>
       <c r="C20">
-        <v>0.3676881734525956</v>
+        <v>0.00393859831980109</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.1905812234209297</v>
+        <v>-0.4916171443657386</v>
       </c>
       <c r="C21">
-        <v>-0.2028465742773175</v>
+        <v>-0.6101114288003946</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.8565148809399451</v>
+        <v>0.3472525446728146</v>
       </c>
       <c r="C22">
-        <v>0.09641747004438411</v>
+        <v>2.307460027319441</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>2.437129718390678</v>
+        <v>-1.19533051297724</v>
       </c>
       <c r="C23">
-        <v>-0.7333276739290934</v>
+        <v>-1.303005424616111</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.171719931631145</v>
+        <v>0.6589286631793597</v>
       </c>
       <c r="C24">
-        <v>0.05717468950796512</v>
+        <v>-1.49582452989852</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.4366624139004878</v>
+        <v>-0.5709520963688538</v>
       </c>
       <c r="C25">
-        <v>0.1199574989693418</v>
+        <v>0.5249501460354515</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.09469939619796988</v>
+        <v>0.3892298788330653</v>
       </c>
       <c r="C26">
-        <v>-0.8703831025193749</v>
+        <v>0.5849056864730464</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.4536642501932912</v>
+        <v>-0.474516581063341</v>
       </c>
       <c r="C27">
-        <v>-0.6560795548281245</v>
+        <v>1.006899748497498</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.8011615737585932</v>
+        <v>-1.5544302895141</v>
       </c>
       <c r="C28">
-        <v>-2.765664656337392</v>
+        <v>-0.5478692585157574</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-1.833815533615838</v>
+        <v>-0.6003579478851528</v>
       </c>
       <c r="C29">
-        <v>2.163392700174747</v>
+        <v>-0.0755325418679027</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>1.279874210777611</v>
+        <v>-0.7325494570952313</v>
       </c>
       <c r="C30">
-        <v>-0.9064347116476279</v>
+        <v>0.6719018906951151</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.4525259658837175</v>
+        <v>0.70388914429314</v>
       </c>
       <c r="C31">
-        <v>-1.25623950379943</v>
+        <v>-1.038428326079031</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-1.337555457768478</v>
+        <v>-0.8879841782971034</v>
       </c>
       <c r="C32">
-        <v>-0.6388451651078726</v>
+        <v>3.320555475160248</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.6966826700407938</v>
+        <v>0.09638493469090673</v>
       </c>
       <c r="C33">
-        <v>-1.025578653496026</v>
+        <v>-0.6503003843968479</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.4278910516166893</v>
+        <v>-1.230204279455413</v>
       </c>
       <c r="C34">
-        <v>-1.699516881128663</v>
+        <v>1.878386044876678</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.568487353890346</v>
+        <v>-0.7186416264737786</v>
       </c>
       <c r="C35">
-        <v>-1.701161271293036</v>
+        <v>-0.02111083566380262</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.816209050337669</v>
+        <v>0.3788183182267908</v>
       </c>
       <c r="C36">
-        <v>-0.6264161129973066</v>
+        <v>0.9967039920327643</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.1442554781366784</v>
+        <v>-1.343458536234192</v>
       </c>
       <c r="C37">
-        <v>0.1117288936217079</v>
+        <v>-0.7406767952560047</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.6148861164228252</v>
+        <v>0.06124594975490342</v>
       </c>
       <c r="C38">
-        <v>-0.3366385685360511</v>
+        <v>0.05608323652061761</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>1.613675165059458</v>
+        <v>-0.8493383116960338</v>
       </c>
       <c r="C39">
-        <v>-0.2736359648546257</v>
+        <v>0.4702685464834576</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.09131446922308833</v>
+        <v>2.08751672244296</v>
       </c>
       <c r="C40">
-        <v>-0.6187011050476309</v>
+        <v>-0.6843692336003325</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.821594015043657</v>
+        <v>-0.8733418613902079</v>
       </c>
       <c r="C41">
-        <v>1.819994248060613</v>
+        <v>1.416731373152817</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.3241505867528988</v>
+        <v>-0.7916014814324964</v>
       </c>
       <c r="C42">
-        <v>0.2995870189033168</v>
+        <v>0.02813484160962465</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.2439834704428099</v>
+        <v>-0.144216847029534</v>
       </c>
       <c r="C43">
-        <v>-0.3273661100168233</v>
+        <v>-0.8397199317984417</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.4890087124139674</v>
+        <v>0.1603976005117016</v>
       </c>
       <c r="C44">
-        <v>-0.8882636169423528</v>
+        <v>0.9285176330607353</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.7673578742522651</v>
+        <v>0.5447448718242794</v>
       </c>
       <c r="C45">
-        <v>-1.360969358344983</v>
+        <v>-1.157363673687578</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.7984179031738202</v>
+        <v>-1.109028489707723</v>
       </c>
       <c r="C46">
-        <v>0.39565167645962</v>
+        <v>0.8641267754121742</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.5826265497807678</v>
+        <v>-0.9683828366049031</v>
       </c>
       <c r="C47">
-        <v>0.6056917550466946</v>
+        <v>1.210540821503681</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.181770043084728</v>
+        <v>-0.06401775356119312</v>
       </c>
       <c r="C48">
-        <v>0.06680292131054082</v>
+        <v>0.4425806061971553</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.5973847046339101</v>
+        <v>0.04944262118261412</v>
       </c>
       <c r="C49">
-        <v>0.5140066270606323</v>
+        <v>-0.2062607524491741</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.7556470496055472</v>
+        <v>0.6882620074725798</v>
       </c>
       <c r="C50">
-        <v>-1.121921106472731</v>
+        <v>-1.272909935142757</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.6292180155461179</v>
+        <v>-1.327452022877538</v>
       </c>
       <c r="C51">
-        <v>-2.33316633130812</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>0.3038979496917634</v>
-      </c>
-      <c r="C52">
-        <v>0.444120512707722</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-1.596657880066003</v>
-      </c>
-      <c r="C53">
-        <v>-0.5516436862030855</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>0.9869684533346416</v>
-      </c>
-      <c r="C54">
-        <v>-0.7926549640105287</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>-0.3440300825641492</v>
-      </c>
-      <c r="C55">
-        <v>-0.1686015801358916</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>0.4325108223151846</v>
-      </c>
-      <c r="C56">
-        <v>1.691923503362422</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>0.07034752875577502</v>
-      </c>
-      <c r="C57">
-        <v>-0.2459286822027217</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>1.110716053568148</v>
-      </c>
-      <c r="C58">
-        <v>-1.251893536224423</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>0.8935758483479749</v>
-      </c>
-      <c r="C59">
-        <v>-0.8072844819209714</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>-0.4478479195323339</v>
-      </c>
-      <c r="C60">
-        <v>1.638829030400702</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>0.1502149105453598</v>
-      </c>
-      <c r="C61">
-        <v>0.3615137551812583</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>-0.3585526437848192</v>
-      </c>
-      <c r="C62">
-        <v>-0.9351322301653597</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>1.083883641098938</v>
-      </c>
-      <c r="C63">
-        <v>-1.235624469993971</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>-0.6322277308200972</v>
-      </c>
-      <c r="C64">
-        <v>1.638972253881713</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>-0.1593498906518523</v>
-      </c>
-      <c r="C65">
-        <v>-0.5366137030684112</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>0.02928965676456951</v>
-      </c>
-      <c r="C66">
-        <v>-0.4906829428877867</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>1.260921293151428</v>
-      </c>
-      <c r="C67">
-        <v>-0.1734017679564836</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>0.1153041814373997</v>
-      </c>
-      <c r="C68">
-        <v>1.135158961164864</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>-0.334641552504809</v>
-      </c>
-      <c r="C69">
-        <v>0.03405758118538925</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>0.09694934157869702</v>
-      </c>
-      <c r="C70">
-        <v>-0.1350028400937517</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>-0.03518289344001641</v>
-      </c>
-      <c r="C71">
-        <v>0.9772190784655439</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>1.22562551527207</v>
-      </c>
-      <c r="C72">
-        <v>0.3912845536279791</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>1.777047680280154</v>
-      </c>
-      <c r="C73">
-        <v>0.3838141046838822</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>-1.65768228523114</v>
-      </c>
-      <c r="C74">
-        <v>2.128261017593754</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-1.957818381865841</v>
-      </c>
-      <c r="C75">
-        <v>1.380149594888405</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>0.04470195034666549</v>
-      </c>
-      <c r="C76">
-        <v>0.1323451798946638</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-0.5956499710906121</v>
-      </c>
-      <c r="C77">
-        <v>-0.8596247866470674</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>0.913598403995013</v>
-      </c>
-      <c r="C78">
-        <v>-0.840577084510987</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>0.06460800846009562</v>
-      </c>
-      <c r="C79">
-        <v>-0.9664279742703519</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>0.7441016950349006</v>
-      </c>
-      <c r="C80">
-        <v>-2.105845451259285</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>1.100222752574025</v>
-      </c>
-      <c r="C81">
-        <v>-0.6917907109326265</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>0.9172989589153484</v>
-      </c>
-      <c r="C82">
-        <v>-0.0608499808268641</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>1.62882252481171</v>
-      </c>
-      <c r="C83">
-        <v>0.8514288761486274</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>1.82104711854953</v>
-      </c>
-      <c r="C84">
-        <v>-1.543596151887207</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-1.725121677168106</v>
-      </c>
-      <c r="C85">
-        <v>1.470357831305696</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-1.502909670512356</v>
-      </c>
-      <c r="C86">
-        <v>-0.5004099044976089</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>-0.4442353667490043</v>
-      </c>
-      <c r="C87">
-        <v>-0.5789014568381894</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>0.3029861141079972</v>
-      </c>
-      <c r="C88">
-        <v>-1.518346651561685</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>-0.5940546432384824</v>
-      </c>
-      <c r="C89">
-        <v>-1.06133189316366</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-0.4120362545178114</v>
-      </c>
-      <c r="C90">
-        <v>0.8996851064572235</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>1.951997395606802</v>
-      </c>
-      <c r="C91">
-        <v>-0.04456494829150714</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>0.8113874948805513</v>
-      </c>
-      <c r="C92">
-        <v>-1.14928181372585</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>0.5524943214291256</v>
-      </c>
-      <c r="C93">
-        <v>-0.9386347793437066</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>-0.01276763576685322</v>
-      </c>
-      <c r="C94">
-        <v>0.1916050121986823</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>0.6759080799900321</v>
-      </c>
-      <c r="C95">
-        <v>-0.05053886479516548</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>-0.05058107448044919</v>
-      </c>
-      <c r="C96">
-        <v>0.3216639088891308</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>-0.7603975224973045</v>
-      </c>
-      <c r="C97">
-        <v>1.294972718450257</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>-1.525968722478349</v>
-      </c>
-      <c r="C98">
-        <v>1.985169135085372</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>0.2829651148016456</v>
-      </c>
-      <c r="C99">
-        <v>-1.474833331279323</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>0.7356123328728751</v>
-      </c>
-      <c r="C100">
-        <v>-0.7635130710224481</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>0.4155064605392436</v>
-      </c>
-      <c r="C101">
-        <v>0.2825928400091966</v>
+        <v>-0.6476653674850024</v>
       </c>
     </row>
   </sheetData>
